--- a/k_12_forms/005_discipline_referral_form--k_12_forms.xlsx
+++ b/k_12_forms/005_discipline_referral_form--k_12_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'student',_'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Student', 'value': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'non-student',_'value':_'non-student'}</t>
+          <t>non-student</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Non-Student', 'value': 'Non-Student'}</t>
+          <t>Non-Student</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'bullying',_'value':_'bullying'}</t>
+          <t>bullying</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Bullying', 'value': 'Bullying'}</t>
+          <t>Bullying</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'fighting',_'value':_'fighting'}</t>
+          <t>fighting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Fighting', 'value': 'Fighting'}</t>
+          <t>Fighting</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'verbal_warning',_'value':_'verbal_warning'}</t>
+          <t>verbal_warning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Verbal Warning', 'value': 'Verbal Warning'}</t>
+          <t>Verbal Warning</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'written_warning',_'value':_'written_warning'}</t>
+          <t>written_warning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Written Warning', 'value': 'Written Warning'}</t>
+          <t>Written Warning</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'detention',_'value':_'detention'}</t>
+          <t>detention</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Detention', 'value': 'Detention'}</t>
+          <t>Detention</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'4',_'label':_'parent_contact',_'value':_'parent_contact'}</t>
+          <t>parent_contact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '4', 'label': 'Parent Contact', 'value': 'Parent Contact'}</t>
+          <t>Parent Contact</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'5',_'label':_'suspended',_'value':_'suspended'}</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '5', 'label': 'Suspended', 'value': 'Suspended'}</t>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'6',_'label':_'removed',_'value':_'removed'}</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '6', 'label': 'Removed', 'value': 'Removed'}</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'9',_'label':_'9th_grade',_'value':_'9th'}</t>
+          <t>9th_grade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '9', 'label': '9th Grade', 'value': '9th'}</t>
+          <t>9th Grade</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'10',_'label':_'10th_grade',_'value':_'10th'}</t>
+          <t>10th_grade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '10', 'label': '10th Grade', 'value': '10th'}</t>
+          <t>10th Grade</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'11',_'label':_'11th_grade',_'value':_'11th'}</t>
+          <t>11th_grade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '11', 'label': '11th Grade', 'value': '11th'}</t>
+          <t>11th Grade</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'12',_'label':_'12th_grade',_'value':_'12th'}</t>
+          <t>12th_grade</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '12', 'label': '12th Grade', 'value': '12th'}</t>
+          <t>12th Grade</t>
         </is>
       </c>
     </row>
